--- a/rules/CORE-000885/positive/01/data/unit-test-coreid-FB2302-positive.xlsx
+++ b/rules/CORE-000885/positive/01/data/unit-test-coreid-FB2302-positive.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sanofinam-my.sharepoint.com/personal/malini_narreddy_sanofi_com/Documents/Desktop/Imp links/SDTM CIDSC documents/CDISC CORE project/FB2302_awaiting qc/positive/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulieChason\GitHub\core-contributor\rules\CORE-000885\positive\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="390" documentId="8_{4BA1E5BB-E5E0-4FA7-809B-87F8E9DC4DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8730FAB-4A24-4D15-9640-BD6D46B74FA9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D40023C-E25E-409A-B536-E0262856B292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{E84A5625-D8F6-4FB6-94ED-5413F497365D}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9772" activeTab="2" xr2:uid="{E84A5625-D8F6-4FB6-94ED-5413F497365D}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="4" r:id="rId1"/>
@@ -861,16 +861,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -893,36 +890,45 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1340,9 +1346,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39D5C60B-7D2C-4EC2-90C9-FC331856666A}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1350,11 +1356,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>223</v>
       </c>
     </row>
@@ -1366,13 +1372,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C5DEA90-A259-4FF8-84C3-0BEFD4EAEE66}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="20.54296875" customWidth="1"/>
+    <col min="2" max="2" width="20.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1380,7 +1386,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>104</v>
       </c>
@@ -1388,7 +1394,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1396,7 +1402,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1412,533 +1418,689 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58540389-4E47-4E49-92C6-7400ED54613C}">
-  <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="11" width="20.7265625" style="11" customWidth="1"/>
-    <col min="12" max="16384" width="8.81640625" style="12"/>
+    <col min="1" max="11" width="20.69140625" style="10" customWidth="1"/>
+    <col min="12" max="16384" width="8.84375" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="10" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="11" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:11" s="10" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="6" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="7" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="D3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A4" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>8</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>50</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>50</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>50</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>50</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>50</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="6">
         <v>50</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="6">
         <v>50</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="6">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:11" s="21" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A5" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13" t="s">
+      <c r="D5" s="20"/>
+      <c r="E5" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-    </row>
-    <row r="6" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+    </row>
+    <row r="6" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13" t="s">
+      <c r="D6" s="20"/>
+      <c r="E6" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13" t="s">
+      <c r="H6" s="20"/>
+      <c r="I6" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:11" s="21" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A7" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15" t="s">
+      <c r="D7" s="22"/>
+      <c r="E7" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15" t="s">
+      <c r="H7" s="22"/>
+      <c r="I7" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="17" t="s">
+    <row r="8" spans="1:11" s="21" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A8" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13" t="s">
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13" t="s">
+      <c r="G8" s="20"/>
+      <c r="H8" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-    </row>
-    <row r="9" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="17" t="s">
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+    </row>
+    <row r="9" spans="1:11" s="21" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A9" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13" t="s">
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13" t="s">
+      <c r="H9" s="20"/>
+      <c r="I9" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-    </row>
-    <row r="10" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="17" t="s">
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+    </row>
+    <row r="10" spans="1:11" s="21" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A10" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13" t="s">
+      <c r="H10" s="20"/>
+      <c r="I10" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="K10" s="20" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="17" t="s">
+    <row r="11" spans="1:11" s="21" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A11" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13" t="s">
+      <c r="H11" s="20"/>
+      <c r="I11" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="20" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="17" t="s">
+    <row r="12" spans="1:11" s="21" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A12" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-    </row>
-    <row r="13" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="17" t="s">
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+    </row>
+    <row r="13" spans="1:11" s="21" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A13" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-    </row>
-    <row r="14" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="17" t="s">
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="19" t="s">
+      <c r="D14" s="20"/>
+      <c r="E14" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13" t="s">
+      <c r="H14" s="20"/>
+      <c r="I14" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="K14" s="20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="17" t="s">
+    <row r="15" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13" t="s">
+      <c r="D15" s="20"/>
+      <c r="E15" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13" t="s">
+      <c r="H15" s="20"/>
+      <c r="I15" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="J15" s="13" t="s">
+      <c r="J15" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="K15" s="13" t="s">
+      <c r="K15" s="20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="17" t="s">
+    <row r="16" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13" t="s">
+      <c r="D16" s="20"/>
+      <c r="E16" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13" t="s">
+      <c r="H16" s="20"/>
+      <c r="I16" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="J16" s="13" t="s">
+      <c r="J16" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="K16" s="13" t="s">
+      <c r="K16" s="20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="17" t="s">
+    <row r="17" spans="1:11" s="21" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A17" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13" t="s">
+      <c r="D17" s="20"/>
+      <c r="E17" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13" t="s">
+      <c r="H17" s="20"/>
+      <c r="I17" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="J17" s="13" t="s">
+      <c r="J17" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="K17" s="13" t="s">
+      <c r="K17" s="20" t="s">
         <v>172</v>
       </c>
+    </row>
+    <row r="18" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="25"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+    </row>
+    <row r="19" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="25"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+    </row>
+    <row r="20" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+    </row>
+    <row r="21" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="25"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+    </row>
+    <row r="22" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+    </row>
+    <row r="23" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="25"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+    </row>
+    <row r="24" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="25"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+    </row>
+    <row r="25" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+    </row>
+    <row r="26" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+    </row>
+    <row r="27" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="25"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+    </row>
+    <row r="28" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="25"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+    </row>
+    <row r="29" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1950,31 +2112,31 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{795E7702-96E4-4A0E-BB7C-F4A9CD306A5D}">
-  <dimension ref="A1:Z11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Z14"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" customWidth="1"/>
-    <col min="4" max="4" width="14.54296875" customWidth="1"/>
-    <col min="5" max="5" width="19.54296875" customWidth="1"/>
+    <col min="1" max="2" width="9.4609375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.69140625" customWidth="1"/>
+    <col min="4" max="4" width="14.53515625" customWidth="1"/>
+    <col min="5" max="5" width="19.53515625" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.453125" customWidth="1"/>
-    <col min="9" max="9" width="17.1796875" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="16.1796875" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="14.453125" hidden="1" customWidth="1"/>
-    <col min="12" max="13" width="8.7265625" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="12.81640625" hidden="1" customWidth="1"/>
-    <col min="15" max="19" width="8.7265625" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="17.26953125" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="15.81640625" customWidth="1"/>
-    <col min="23" max="23" width="17.08984375" customWidth="1"/>
-    <col min="24" max="24" width="13.08984375" customWidth="1"/>
-    <col min="25" max="25" width="15.81640625" customWidth="1"/>
-    <col min="26" max="26" width="10.26953125" customWidth="1"/>
+    <col min="7" max="7" width="17.23046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.4609375" customWidth="1"/>
+    <col min="9" max="9" width="17.15234375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="16.15234375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="14.4609375" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="8.69140625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="12.84375" hidden="1" customWidth="1"/>
+    <col min="15" max="19" width="8.69140625" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="17.23046875" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="15.84375" customWidth="1"/>
+    <col min="23" max="23" width="17.07421875" customWidth="1"/>
+    <col min="24" max="24" width="13.07421875" customWidth="1"/>
+    <col min="25" max="25" width="15.84375" customWidth="1"/>
+    <col min="26" max="26" width="10.23046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2047,14 +2209,14 @@
       <c r="X1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Y1" s="9" t="s">
         <v>212</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" s="2" customFormat="1" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
@@ -2134,7 +2296,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>59</v>
       </c>
@@ -2214,17 +2376,17 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>12</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>20</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -2260,7 +2422,7 @@
       <c r="O4" s="1">
         <v>8</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P4" s="4">
         <v>5</v>
       </c>
       <c r="Q4" s="1">
@@ -2294,420 +2456,423 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:26" s="15" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A5" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="M5" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="O5" s="4">
+      <c r="O5" s="14">
         <v>76</v>
       </c>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3" t="s">
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="R5" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="S5" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="T5" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="U5" s="3" t="s">
+      <c r="U5" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="V5" s="3" t="s">
+      <c r="V5" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="W5" s="1" t="s">
+      <c r="W5" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="X5" s="3" t="s">
+      <c r="X5" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="Y5" s="10"/>
-      <c r="Z5" s="1" t="s">
+      <c r="Y5" s="13"/>
+      <c r="Z5" s="13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6" spans="1:26" s="15" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A6" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="1" t="s">
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="N6" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="O6" s="4">
+      <c r="O6" s="14">
         <v>53</v>
       </c>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3" t="s">
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="R6" s="1" t="s">
+      <c r="R6" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="S6" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="T6" s="1" t="s">
+      <c r="T6" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="U6" s="3" t="s">
+      <c r="U6" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="V6" s="3" t="s">
+      <c r="V6" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="W6" s="1" t="s">
+      <c r="W6" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="X6" s="3" t="s">
+      <c r="X6" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="Y6" s="10"/>
-      <c r="Z6" s="1" t="s">
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="13" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:26" s="15" customFormat="1" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A7" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1" t="s">
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="1" t="s">
+      <c r="K7" s="13"/>
+      <c r="L7" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="N7" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="O7" s="4">
+      <c r="O7" s="14">
         <v>70</v>
       </c>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3" t="s">
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="R7" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="S7" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="T7" s="1" t="s">
+      <c r="T7" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3" t="s">
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="Z7" s="1" t="s">
+      <c r="Z7" s="13" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:26" s="15" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A8" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1" t="s">
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="N8" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="O8" s="4">
+      <c r="O8" s="14">
         <v>57</v>
       </c>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3" t="s">
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="R8" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="S8" s="1" t="s">
+      <c r="S8" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="T8" s="1" t="s">
+      <c r="T8" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="U8" s="22" t="s">
+      <c r="U8" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="V8" s="22" t="s">
+      <c r="V8" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="W8" s="22"/>
-      <c r="X8" s="22"/>
-      <c r="Y8" s="22" t="s">
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="Z8" s="1" t="s">
+      <c r="Z8" s="13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="9" spans="1:26" s="15" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A9" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1" t="s">
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M9" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="N9" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="O9" s="4">
+      <c r="O9" s="14">
         <v>57</v>
       </c>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3" t="s">
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="R9" s="1" t="s">
+      <c r="R9" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="S9" s="1" t="s">
+      <c r="S9" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="T9" s="1" t="s">
+      <c r="T9" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="22"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="22" t="s">
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="Z9" s="1" t="s">
+      <c r="Z9" s="13" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="10" spans="1:26" s="15" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A10" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="1" t="s">
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="N10" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="O10" s="4">
+      <c r="O10" s="14">
         <v>54</v>
       </c>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3" t="s">
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="R10" s="1" t="s">
+      <c r="R10" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="S10" s="1" t="s">
+      <c r="S10" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="T10" s="1" t="s">
+      <c r="T10" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="U10" s="10" t="s">
+      <c r="U10" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="V10" s="10" t="s">
+      <c r="V10" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="W10" s="10" t="s">
+      <c r="W10" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="X10" s="10" t="s">
+      <c r="X10" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="Y10" s="10" t="s">
+      <c r="Y10" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="Z10" s="1" t="s">
+      <c r="Z10" s="13" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="D11" s="20"/>
-      <c r="E11" s="21"/>
-    </row>
+    <row r="11" spans="1:26" s="12" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="D11" s="17"/>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:26" s="12" customFormat="1" x14ac:dyDescent="0.4"/>
+    <row r="13" spans="1:26" s="12" customFormat="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="1:26" s="12" customFormat="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <conditionalFormatting sqref="A2:AA4">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
@@ -2721,427 +2886,445 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FFAAC06-8AA1-4098-9728-071939A44F17}">
-  <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O10"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="20.90625" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" customWidth="1"/>
-    <col min="10" max="10" width="27.1796875" customWidth="1"/>
-    <col min="12" max="12" width="20.54296875" customWidth="1"/>
-    <col min="13" max="13" width="16.81640625" customWidth="1"/>
+    <col min="3" max="3" width="20.921875" customWidth="1"/>
+    <col min="5" max="5" width="13.53515625" customWidth="1"/>
+    <col min="10" max="10" width="27.15234375" customWidth="1"/>
+    <col min="12" max="12" width="20.53515625" customWidth="1"/>
+    <col min="13" max="13" width="16.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:15" ht="29.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:15" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="7" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" s="7" t="s">
+      <c r="E3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="N3" s="7" t="s">
+      <c r="H3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N3" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A4" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>8</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>50</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>50</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>8</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>50</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="6">
         <v>50</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="6">
         <v>50</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="6">
         <v>50</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="6">
         <v>8</v>
       </c>
-      <c r="O4" s="7">
+      <c r="O4" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="12">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="12">
         <v>20.118343195266299</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="M5" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="12">
         <v>1</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="12">
         <v>2</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="12">
         <v>20</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="M6" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="12">
         <v>1</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="12">
         <v>1</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="12">
         <v>20.338983050847499</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="12">
         <v>1</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="12">
         <v>2</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="12">
         <v>20</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="12">
         <v>1</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="9" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="12">
         <v>1</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="12">
         <v>15</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M9" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="12">
         <v>1</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="12">
         <v>1</v>
       </c>
     </row>
+    <row r="10" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010090ADB40D834AE945B19FCDA4041AC0CB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c09bae7b217a3930fedb3a6204001e96">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xmlns:ns3="63ea592b-d684-45c7-8cdc-fad8f8e6bb41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac018b55a0c98af8ca0cc741473a0b1c" ns2:_="" ns3:_="">
     <xsd:import namespace="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
@@ -3364,24 +3547,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A58D54F7-511B-43F8-921F-D11D7692FD68}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70C9EDA2-6184-4936-95C4-1B27C2EDFE85}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDB34C10-3C7D-45BB-9EE8-48CD7918EE6D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3398,22 +3582,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70C9EDA2-6184-4936-95C4-1B27C2EDFE85}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A58D54F7-511B-43F8-921F-D11D7692FD68}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>